--- a/public/format.xlsx
+++ b/public/format.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\solo_amalfatimah\public\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA527A47-3CAB-433B-A719-4E91FE9EFC7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED65E7C-E897-47C6-8FAF-F53E5BF726F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
   <si>
     <t>NIS</t>
   </si>
@@ -49,12 +49,6 @@
     <t>ALAMAT</t>
   </si>
   <si>
-    <t>AYAH</t>
-  </si>
-  <si>
-    <t>IBU</t>
-  </si>
-  <si>
     <t>Kontakwali</t>
   </si>
   <si>
@@ -79,9 +73,6 @@
     <t>Sehun</t>
   </si>
   <si>
-    <t>Irene</t>
-  </si>
-  <si>
     <t>081234567891</t>
   </si>
   <si>
@@ -104,6 +95,9 @@
   </si>
   <si>
     <t>Amal Fatimah</t>
+  </si>
+  <si>
+    <t>WALI</t>
   </si>
 </sst>
 </file>
@@ -519,14 +513,12 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
+      <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
@@ -535,38 +527,36 @@
         <v>123456700</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C2" s="2">
         <v>123456700</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
     </row>
@@ -575,38 +565,36 @@
         <v>123456701</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="C3" s="2">
         <v>123456701</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
     </row>
@@ -615,38 +603,36 @@
         <v>123456702</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="C4" s="2">
         <v>123456702</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G4" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="I4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
     </row>
@@ -655,38 +641,36 @@
         <v>123456703</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C5" s="2">
         <v>123456703</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
     </row>
@@ -695,38 +679,36 @@
         <v>123456704</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C6" s="2">
         <v>123456704</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="3" t="s">
+      <c r="H6" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
     </row>
@@ -735,38 +717,36 @@
         <v>123456705</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C7" s="2">
         <v>123456705</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="I7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>20</v>
-      </c>
+      <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
     </row>

--- a/public/format.xlsx
+++ b/public/format.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\laragon\www\solo_amalfatimah\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ED65E7C-E897-47C6-8FAF-F53E5BF726F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09F8365B-FEE1-4759-877E-AAD6A49B6C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="24">
   <si>
     <t>NIS</t>
   </si>
@@ -49,9 +49,6 @@
     <t>ALAMAT</t>
   </si>
   <si>
-    <t>Kontakwali</t>
-  </si>
-  <si>
     <t>Test ICT 1</t>
   </si>
   <si>
@@ -71,9 +68,6 @@
   </si>
   <si>
     <t>Sehun</t>
-  </si>
-  <si>
-    <t>081234567891</t>
   </si>
   <si>
     <t>Test ICT 2</t>
@@ -513,11 +507,9 @@
         <v>8</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>9</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
@@ -527,35 +519,33 @@
         <v>123456700</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="2">
         <v>123456700</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -565,35 +555,33 @@
         <v>123456701</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C3" s="2">
         <v>123456701</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
       <c r="N3" s="1"/>
@@ -603,35 +591,33 @@
         <v>123456702</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" s="2">
         <v>123456702</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="H4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="J4" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
       <c r="N4" s="1"/>
@@ -641,35 +627,33 @@
         <v>123456703</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" s="2">
         <v>123456703</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G5" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K5" s="1"/>
       <c r="L5" s="1"/>
       <c r="M5" s="1"/>
       <c r="N5" s="1"/>
@@ -679,35 +663,33 @@
         <v>123456704</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="2">
         <v>123456704</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="3" t="s">
-        <v>13</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="J6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
       <c r="N6" s="1"/>
@@ -717,35 +699,33 @@
         <v>123456705</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C7" s="2">
         <v>123456705</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="G7" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="H7" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H7" s="2" t="s">
+      <c r="I7" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="J7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>17</v>
-      </c>
+      <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="1"/>
       <c r="N7" s="1"/>
